--- a/diseases/d002/2000-2004.xlsx
+++ b/diseases/d002/2000-2004.xlsx
@@ -5067,9 +5067,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5511,9 +5508,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5955,9 +5949,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6399,9 +6390,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6843,9 +6831,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7287,9 +7272,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7731,9 +7713,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8175,9 +8154,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -8619,9 +8595,6 @@
       <c r="O54" t="n">
         <v>158</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.3358595926643844</v>
       </c>
@@ -9063,9 +9036,6 @@
       <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.004251387248916258</v>
       </c>
@@ -9507,9 +9477,6 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.002125693624458129</v>
       </c>
@@ -9951,9 +9918,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10622,9 +10586,6 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -11066,9 +11027,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -11510,9 +11468,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11954,9 +11909,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12398,9 +12350,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.002114204216545633</v>
       </c>
@@ -12842,9 +12791,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -13286,9 +13232,6 @@
       <c r="O85" t="n">
         <v>2</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.004228408433091266</v>
       </c>
@@ -13730,9 +13673,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14174,9 +14114,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14618,9 +14555,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -15062,9 +14996,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15506,9 +15437,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16177,9 +16105,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.002104635732751713</v>
       </c>
@@ -16621,9 +16546,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17065,9 +16987,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -17509,9 +17428,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17953,9 +17869,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -18397,9 +18310,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18841,9 +18751,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -19285,9 +19192,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19729,9 +19633,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -20173,9 +20074,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -20617,9 +20515,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -21061,9 +20956,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -21880,9 +21772,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -22324,9 +22213,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -22768,9 +22654,6 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -23212,9 +23095,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -23656,9 +23536,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -24100,9 +23977,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.002096564599647205</v>
       </c>
@@ -24544,9 +24418,6 @@
       <c r="O160" t="n">
         <v>5</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.01048282299823602</v>
       </c>
@@ -25136,9 +25007,6 @@
       <c r="O164" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -25580,9 +25448,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -26024,9 +25889,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -26468,9 +26330,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -26911,9 +26770,6 @@
       </c>
       <c r="O176" t="n">
         <v>1</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0.002096564599647205</v>
